--- a/analysis_sample1.xlsx
+++ b/analysis_sample1.xlsx
@@ -3727,7 +3727,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -3739,8 +3739,11 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3750,6 +3753,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
       </patternFill>
     </fill>
     <fill>
@@ -3775,11 +3783,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4216,7 +4226,7 @@
       <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K2">
@@ -4248,7 +4258,7 @@
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -4278,7 +4288,7 @@
       <c r="K3">
         <v>0.6</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M3" t="s">
@@ -4293,10 +4303,10 @@
       <c r="P3">
         <v>2</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="2">
         <v>193</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="3">
         <v>0.56</v>
       </c>
     </row>
@@ -4331,7 +4341,7 @@
       <c r="J4" t="s">
         <v>45</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>0.36</v>
       </c>
       <c r="L4" t="s">
@@ -4416,7 +4426,7 @@
       <c r="A6" t="s">
         <v>57</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" t="s">
@@ -4431,7 +4441,7 @@
       <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>58</v>
       </c>
       <c r="H6" t="s">
@@ -4440,13 +4450,13 @@
       <c r="I6" t="s">
         <v>60</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K6">
         <v>0.93</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="2" t="s">
         <v>61</v>
       </c>
       <c r="M6" t="s">
@@ -4464,7 +4474,7 @@
       <c r="Q6">
         <v>61</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="3">
         <v>0.7</v>
       </c>
     </row>
@@ -4499,7 +4509,7 @@
       <c r="J7" t="s">
         <v>70</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>0.49</v>
       </c>
       <c r="L7" t="s">
@@ -4543,7 +4553,7 @@
       <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H8" t="s">
@@ -4552,13 +4562,13 @@
       <c r="I8" t="s">
         <v>76</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K8">
         <v>0.26</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="M8" t="s">
@@ -4573,10 +4583,10 @@
       <c r="P8">
         <v>10</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="2">
         <v>102</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="3">
         <v>0.59</v>
       </c>
     </row>
@@ -4584,7 +4594,7 @@
       <c r="A9" t="s">
         <v>80</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" t="s">
@@ -4599,7 +4609,7 @@
       <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H9" t="s">
@@ -4608,13 +4618,13 @@
       <c r="I9" t="s">
         <v>84</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="2" t="s">
         <v>85</v>
       </c>
       <c r="K9">
         <v>0.9</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="2" t="s">
         <v>86</v>
       </c>
       <c r="M9" t="s">
@@ -4632,7 +4642,7 @@
       <c r="Q9">
         <v>64</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="3">
         <v>0.7</v>
       </c>
     </row>
@@ -4685,7 +4695,7 @@
       <c r="P10">
         <v>2.7</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="2">
         <v>139</v>
       </c>
       <c r="R10">
@@ -4726,7 +4736,7 @@
       <c r="K11">
         <v>0.22</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="M11" t="s">
@@ -4808,7 +4818,7 @@
       <c r="A13" t="s">
         <v>115</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>5</v>
       </c>
       <c r="C13" t="s">
@@ -4823,7 +4833,7 @@
       <c r="F13" t="s">
         <v>22</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
         <v>117</v>
       </c>
       <c r="H13" t="s">
@@ -4838,7 +4848,7 @@
       <c r="K13">
         <v>0.34</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="2" t="s">
         <v>121</v>
       </c>
       <c r="M13" t="s">
@@ -4864,7 +4874,7 @@
       <c r="A14" t="s">
         <v>123</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>6</v>
       </c>
       <c r="C14" t="s">
@@ -4891,7 +4901,7 @@
       <c r="J14" t="s">
         <v>130</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>0.34</v>
       </c>
       <c r="L14" t="s">
@@ -4947,7 +4957,7 @@
       <c r="J15" t="s">
         <v>139</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>0.61</v>
       </c>
       <c r="L15" t="s">
@@ -5059,7 +5069,7 @@
       <c r="J17" t="s">
         <v>158</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>0.39</v>
       </c>
       <c r="L17" t="s">
@@ -5103,7 +5113,7 @@
       <c r="F18" t="s">
         <v>22</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="2" t="s">
         <v>164</v>
       </c>
       <c r="H18" t="s">
@@ -5112,7 +5122,7 @@
       <c r="I18" t="s">
         <v>166</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="2" t="s">
         <v>167</v>
       </c>
       <c r="K18">
@@ -5200,7 +5210,7 @@
       <c r="A20" t="s">
         <v>180</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>2</v>
       </c>
       <c r="C20" t="s">
@@ -5215,7 +5225,7 @@
       <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="2" t="s">
         <v>181</v>
       </c>
       <c r="H20" t="s">
@@ -5230,7 +5240,7 @@
       <c r="K20">
         <v>0.64</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="2" t="s">
         <v>185</v>
       </c>
       <c r="M20" t="s">
@@ -5245,10 +5255,10 @@
       <c r="P20">
         <v>2</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="2">
         <v>151</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="3">
         <v>0.71</v>
       </c>
     </row>
@@ -5256,7 +5266,7 @@
       <c r="A21" t="s">
         <v>187</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>6</v>
       </c>
       <c r="C21" t="s">
@@ -5357,7 +5367,7 @@
       <c r="P22">
         <v>4</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="2">
         <v>113</v>
       </c>
       <c r="R22">
@@ -5383,7 +5393,7 @@
       <c r="F23" t="s">
         <v>136</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="2" t="s">
         <v>204</v>
       </c>
       <c r="H23" t="s">
@@ -5392,7 +5402,7 @@
       <c r="I23" t="s">
         <v>206</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="2" t="s">
         <v>207</v>
       </c>
       <c r="K23">
@@ -5413,7 +5423,7 @@
       <c r="P23">
         <v>3.5</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="2">
         <v>132</v>
       </c>
       <c r="R23">
@@ -5448,10 +5458,10 @@
       <c r="I24" t="s">
         <v>214</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="2">
         <v>0.42</v>
       </c>
       <c r="L24" t="s">
@@ -5510,7 +5520,7 @@
       <c r="K25">
         <v>0.28</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" s="2" t="s">
         <v>222</v>
       </c>
       <c r="M25" t="s">
@@ -5648,7 +5658,7 @@
       <c r="A28" t="s">
         <v>239</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <v>3</v>
       </c>
       <c r="C28" t="s">
@@ -5731,7 +5741,7 @@
       <c r="J29" t="s">
         <v>251</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="2">
         <v>0.36</v>
       </c>
       <c r="L29" t="s">
@@ -5816,7 +5826,7 @@
       <c r="A31" t="s">
         <v>262</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
         <v>5</v>
       </c>
       <c r="C31" t="s">
@@ -5840,7 +5850,7 @@
       <c r="I31" t="s">
         <v>267</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="2" t="s">
         <v>268</v>
       </c>
       <c r="K31">
@@ -5872,7 +5882,7 @@
       <c r="A32" t="s">
         <v>271</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
         <v>1</v>
       </c>
       <c r="C32" t="s">
@@ -5917,7 +5927,7 @@
       <c r="P32">
         <v>1</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="2">
         <v>209</v>
       </c>
       <c r="R32">
@@ -5928,7 +5938,7 @@
       <c r="A33" t="s">
         <v>278</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
         <v>6</v>
       </c>
       <c r="C33" t="s">
@@ -6055,7 +6065,7 @@
       <c r="F35" t="s">
         <v>22</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="2" t="s">
         <v>298</v>
       </c>
       <c r="H35" t="s">
@@ -6064,7 +6074,7 @@
       <c r="I35" t="s">
         <v>300</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="2" t="s">
         <v>301</v>
       </c>
       <c r="K35">
@@ -6152,7 +6162,7 @@
       <c r="A37" t="s">
         <v>311</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="2">
         <v>6</v>
       </c>
       <c r="C37" t="s">
@@ -6179,7 +6189,7 @@
       <c r="J37" t="s">
         <v>315</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="2">
         <v>0.35</v>
       </c>
       <c r="L37" t="s">
@@ -6291,7 +6301,7 @@
       <c r="J39" t="s">
         <v>329</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="2">
         <v>0.62</v>
       </c>
       <c r="L39" t="s">
@@ -6309,7 +6319,7 @@
       <c r="P39">
         <v>4</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="2">
         <v>204</v>
       </c>
       <c r="R39">
@@ -6320,7 +6330,7 @@
       <c r="A40" t="s">
         <v>332</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="2">
         <v>1</v>
       </c>
       <c r="C40" t="s">
@@ -6335,7 +6345,7 @@
       <c r="F40" t="s">
         <v>22</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="2" t="s">
         <v>333</v>
       </c>
       <c r="H40" t="s">
@@ -6350,7 +6360,7 @@
       <c r="K40">
         <v>1</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" s="2" t="s">
         <v>337</v>
       </c>
       <c r="M40" t="s">
@@ -6365,10 +6375,10 @@
       <c r="P40">
         <v>1</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="2">
         <v>161</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="3">
         <v>0.62</v>
       </c>
     </row>
@@ -6376,7 +6386,7 @@
       <c r="A41" t="s">
         <v>338</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="2">
         <v>4</v>
       </c>
       <c r="C41" t="s">
@@ -6391,7 +6401,7 @@
       <c r="F41" t="s">
         <v>339</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="2" t="s">
         <v>340</v>
       </c>
       <c r="H41" t="s">
@@ -6400,7 +6410,7 @@
       <c r="I41" t="s">
         <v>342</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="2" t="s">
         <v>343</v>
       </c>
       <c r="K41">
@@ -6421,10 +6431,10 @@
       <c r="P41">
         <v>2</v>
       </c>
-      <c r="Q41">
+      <c r="Q41" s="2">
         <v>158</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="3">
         <v>0.64</v>
       </c>
     </row>
@@ -6477,7 +6487,7 @@
       <c r="P42">
         <v>3.5</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="2">
         <v>157</v>
       </c>
       <c r="R42">
@@ -6504,26 +6514,26 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>358</v>
       </c>
     </row>
@@ -9517,65 +9527,65 @@
     <col min="17" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>358</v>
       </c>
     </row>
